--- a/data/uniques_OLS.xlsx
+++ b/data/uniques_OLS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,32 +441,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>541</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.01227596366314756</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -576,22 +576,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>0.002203759613901316</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.02203759613901316</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.002203759613901316</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0.002372948388372553</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2284,19 +2284,19 @@
         <v>0.003503485968538696</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.003503485968538696</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">

--- a/data/uniques_OLS.xlsx
+++ b/data/uniques_OLS.xlsx
@@ -446,27 +446,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>799</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>342</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
         </is>
       </c>
     </row>
@@ -554,13 +554,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.02203759613901316</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02203759613901316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -613,13 +613,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.00962186086789185</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00962186086789185</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01465774173059071</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.002372948388372553</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.01529597715800744</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01529597715800744</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1261,19 +1261,19 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.001319574569158903</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>0.00395872370747671</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.003618206816701643</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2290,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">

--- a/data/uniques_OLS.xlsx
+++ b/data/uniques_OLS.xlsx
@@ -451,22 +451,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>410</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>541</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
         </is>
       </c>
     </row>
@@ -554,13 +554,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.01227596366314756</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.02203759613901316</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.00184060371801951</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.002372948388372553</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0.002372948388372553</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.00395872370747671</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0.001319574569158903</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00395872370747671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.003618206816701643</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.003618206816701643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2290,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.003503485968538696</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">

--- a/data/uniques_OLS.xlsx
+++ b/data/uniques_OLS.xlsx
@@ -441,32 +441,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>494</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>201</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
         </is>
       </c>
     </row>
@@ -554,13 +554,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -576,22 +576,22 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02203759613901316</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.02203759613901316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -920,19 +920,19 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.00962186086789185</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -951,19 +951,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.01465774173059071</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1103,19 +1103,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1137,19 +1137,19 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.01529597715800744</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1258,19 +1258,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.00395872370747671</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00395872370747671</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.003618206816701643</v>
       </c>
       <c r="F36" t="n">
-        <v>0.003618206816701643</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>0.003503485968538696</v>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="I60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
